--- a/reports/latest/reports/Excel/Passed_Test_Cases.xlsx
+++ b/reports/latest/reports/Excel/Passed_Test_Cases.xlsx
@@ -854,7 +854,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
@@ -888,7 +888,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
@@ -1024,7 +1024,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
@@ -1296,7 +1296,7 @@
         <v>60</v>
       </c>
       <c r="D28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
@@ -1364,7 +1364,7 @@
         <v>68</v>
       </c>
       <c r="D32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>78</v>
       </c>
       <c r="D37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>8</v>
@@ -1483,7 +1483,7 @@
         <v>82</v>
       </c>
       <c r="D39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>8</v>
@@ -1500,7 +1500,7 @@
         <v>84</v>
       </c>
       <c r="D40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>8</v>
@@ -1585,7 +1585,7 @@
         <v>94</v>
       </c>
       <c r="D45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -1704,7 +1704,7 @@
         <v>108</v>
       </c>
       <c r="D52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>8</v>

--- a/reports/latest/reports/Excel/Passed_Test_Cases.xlsx
+++ b/reports/latest/reports/Excel/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="107">
   <si>
     <t>Test ID</t>
   </si>
@@ -28,370 +28,310 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>TC_PATIENT_001</t>
-  </si>
-  <si>
-    <t>Patient Management</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_001 — Patient management scenario 1</t>
+    <t>TC_SURVEY_001</t>
+  </si>
+  <si>
+    <t>Surveys</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_001 — Survey scenario 1</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>TC_PATIENT_002</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_002 — Patient management scenario 2</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_003</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_003 — Patient management scenario 3</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_004</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_004 — Patient management scenario 4</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_005</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_005 — Patient management scenario 5</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_006</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_006 — Patient management scenario 6</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_007</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_007 — Patient management scenario 7</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_008</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_008 — Patient management scenario 8</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_009</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_009 — Patient management scenario 9</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_010</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_010 — Patient management scenario 10</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_011</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_011 — Patient management scenario 11</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_012</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_012 — Patient management scenario 12</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_013</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_013 — Patient management scenario 13</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_014</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_014 — Patient management scenario 14</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_015</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_015 — Patient management scenario 15</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_016</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_016 — Patient management scenario 16</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_017</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_017 — Patient management scenario 17</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_018</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_018 — Patient management scenario 18</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_019</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_019 — Patient management scenario 19</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_020</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_020 — Patient management scenario 20</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_021</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_021 — Patient management scenario 21</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_022</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_022 — Patient management scenario 22</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_023</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_023 — Patient management scenario 23</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_024</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_024 — Patient management scenario 24</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_025</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_025 — Patient management scenario 25</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_026</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_026 — Patient management scenario 26</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_027</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_027 — Patient management scenario 27</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_028</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_028 — Patient management scenario 28</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_029</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_029 — Patient management scenario 29</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_030</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_030 — Patient management scenario 30</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_031</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_031 — Patient management scenario 31</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_032</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_032 — Patient management scenario 32</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_033</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_033 — Patient management scenario 33</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_034</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_034 — Patient management scenario 34</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_035</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_035 — Patient management scenario 35</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_036</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_036 — Patient management scenario 36</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_037</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_037 — Patient management scenario 37</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_038</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_038 — Patient management scenario 38</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_039</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_039 — Patient management scenario 39</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_040</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_040 — Patient management scenario 40</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_041</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_041 — Patient management scenario 41</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_042</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_042 — Patient management scenario 42</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_043</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_043 — Patient management scenario 43</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_044</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_044 — Patient management scenario 44</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_045</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_045 — Patient management scenario 45</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_046</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_046 — Patient management scenario 46</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_047</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_047 — Patient management scenario 47</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_048</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_048 — Patient management scenario 48</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_049</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_049 — Patient management scenario 49</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_050</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_050 — Patient management scenario 50</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_051</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_051 — Patient management scenario 51</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_052</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_052 — Patient management scenario 52</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_053</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_053 — Patient management scenario 53</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_054</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_054 — Patient management scenario 54</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_055</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_055 — Patient management scenario 55</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_056</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_056 — Patient management scenario 56</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_057</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_057 — Patient management scenario 57</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_058</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_058 — Patient management scenario 58</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_059</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_059 — Patient management scenario 59</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_060</t>
-  </si>
-  <si>
-    <t>TC_PATIENT_060 — Patient management scenario 60</t>
+    <t>TC_SURVEY_002</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_002 — Survey scenario 2</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_003</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_003 — Survey scenario 3</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_004</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_004 — Survey scenario 4</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_005</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_005 — Survey scenario 5</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_006</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_006 — Survey scenario 6</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_007</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_007 — Survey scenario 7</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_008</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_008 — Survey scenario 8</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_009</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_009 — Survey scenario 9</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_010</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_010 — Survey scenario 10</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_011</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_011 — Survey scenario 11</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_012</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_012 — Survey scenario 12</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_013</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_013 — Survey scenario 13</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_014</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_014 — Survey scenario 14</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_015</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_015 — Survey scenario 15</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_016</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_016 — Survey scenario 16</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_017</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_017 — Survey scenario 17</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_018</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_018 — Survey scenario 18</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_019</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_019 — Survey scenario 19</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_020</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_020 — Survey scenario 20</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_021</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_021 — Survey scenario 21</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_022</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_022 — Survey scenario 22</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_023</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_023 — Survey scenario 23</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_024</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_024 — Survey scenario 24</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_025</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_025 — Survey scenario 25</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_026</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_026 — Survey scenario 26</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_027</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_027 — Survey scenario 27</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_028</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_028 — Survey scenario 28</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_029</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_029 — Survey scenario 29</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_030</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_030 — Survey scenario 30</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_031</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_031 — Survey scenario 31</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_032</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_032 — Survey scenario 32</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_033</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_033 — Survey scenario 33</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_034</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_034 — Survey scenario 34</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_035</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_035 — Survey scenario 35</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_036</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_036 — Survey scenario 36</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_037</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_037 — Survey scenario 37</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_038</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_038 — Survey scenario 38</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_039</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_039 — Survey scenario 39</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_040</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_040 — Survey scenario 40</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_041</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_041 — Survey scenario 41</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_042</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_042 — Survey scenario 42</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_043</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_043 — Survey scenario 43</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_044</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_044 — Survey scenario 44</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_045</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_045 — Survey scenario 45</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_046</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_046 — Survey scenario 46</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_047</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_047 — Survey scenario 47</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_048</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_048 — Survey scenario 48</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_049</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_049 — Survey scenario 49</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_050</t>
+  </si>
+  <si>
+    <t>TC_SURVEY_050 — Survey scenario 50</t>
   </si>
 </sst>
 </file>
@@ -816,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -854,7 +794,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
@@ -922,7 +862,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
@@ -1007,7 +947,7 @@
         <v>26</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>8</v>
@@ -1024,7 +964,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
@@ -1041,7 +981,7 @@
         <v>30</v>
       </c>
       <c r="D13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>8</v>
@@ -1364,7 +1304,7 @@
         <v>68</v>
       </c>
       <c r="D32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>8</v>
@@ -1449,7 +1389,7 @@
         <v>78</v>
       </c>
       <c r="D37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>8</v>
@@ -1483,7 +1423,7 @@
         <v>82</v>
       </c>
       <c r="D39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>8</v>
@@ -1551,7 +1491,7 @@
         <v>90</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>8</v>
@@ -1636,7 +1576,7 @@
         <v>100</v>
       </c>
       <c r="D48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>8</v>
@@ -1690,176 +1630,6 @@
         <v>0</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" s="3">
-        <v>0</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" s="2">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="3">
-        <v>0</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="3">
-        <v>0</v>
-      </c>
-      <c r="E61" s="3" t="s">
         <v>8</v>
       </c>
     </row>
